--- a/docs/returns-analysis-2026-05-27.xlsx
+++ b/docs/returns-analysis-2026-05-27.xlsx
@@ -18,6 +18,10 @@
     <sheet name="Rep x Category" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Order Writers (rep_3)" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="25 Discussion Points" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Reps — Self vs Handoff" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Order Writers (real-prod)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Handoff Pairs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Top SKUs — Rep Breakdown" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,9 +30,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
     <numFmt numFmtId="165" formatCode="0.00&quot;%&quot;"/>
+    <numFmt numFmtId="166" formatCode="+0.00&quot;pp&quot;;-0.00&quot;pp&quot;"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -76,7 +81,7 @@
       <color rgb="00006834"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -101,6 +106,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF5DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -130,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -178,6 +188,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -795,6 +808,54 @@
     <row r="30"/>
     <row r="31"/>
     <row r="32"/>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>12. Reps — Self vs Handoff</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Per-rep diagnostic: own keying vs handed-off keying</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>13. Order Writers (real-prod)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>All rep_3 writers across real-product SKUs</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>14. Handoff Pairs</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>rep_1 → rep_3 mismatches with their return rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>15. Top SKUs — Rep Breakdown</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Per-SKU rep_1 leaderboard for top 15 credit-leakers</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A29:F32"/>
@@ -2682,6 +2743,5632 @@
     <mergeCell ref="A32:E33"/>
     <mergeCell ref="A31:E31"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rep Diagnostic: When the rep keys their own vs when someone else keys for them</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>rep_1 = account owner. Same numerator across both views. Split by who keyed the SO. Real-product SKUs only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Rep</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Total Ship $ (rep_1)</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Total Cred $ (rep_1)</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Total Ret %</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Self-Keyed Ship $</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Self-Keyed Cred $</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Self-Keyed Ret %</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>Other-Keyed Ship $</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>Other-Keyed Cred $</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>Other-Keyed Ret %</t>
+        </is>
+      </c>
+      <c r="K4" s="11" t="inlineStr">
+        <is>
+          <t>Self − Other (pp)</t>
+        </is>
+      </c>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>zacl</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>9224665</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>255103</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>4525066</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>190775</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>4699599</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>64328</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>1.368797635713175</v>
+      </c>
+      <c r="K5" s="27" t="n">
+        <v>2.851202364286825</v>
+      </c>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t>self-keying worse — coach takeoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>mikes</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>8074246</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>451019</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>4838406</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>114853</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>3235840</v>
+      </c>
+      <c r="I6" s="13" t="n">
+        <v>336166</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>10.38883257515823</v>
+      </c>
+      <c r="K6" s="27" t="n">
+        <v>-8.018832575158228</v>
+      </c>
+      <c r="L6" s="28" t="inlineStr">
+        <is>
+          <t>handoff penalty — review shipping lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>garretp</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>6118219</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>334175</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>4332163</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>312045</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>1786056</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>22130</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>1.239042896751278</v>
+      </c>
+      <c r="K7" s="27" t="n">
+        <v>5.960957103248722</v>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t>self-keying worse — coach takeoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>pauln</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>5602579</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>450727</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>4053837</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>404970</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>1548742</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>45757</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>2.954462395931666</v>
+      </c>
+      <c r="K8" s="27" t="n">
+        <v>7.035537604068335</v>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t>self-keying worse — coach takeoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>mattb</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>4973739</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>346712</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>3682511</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>295424</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>1291228</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>51288</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>3.972032824567001</v>
+      </c>
+      <c r="K9" s="27" t="n">
+        <v>4.047967175432999</v>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>self-keying worse — coach takeoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>kevinv</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>4878349</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>353848</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>2802993</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>226757</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>2075356</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>127091</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>6.123816829498168</v>
+      </c>
+      <c r="K10" s="27" t="n">
+        <v>1.966183170501832</v>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t>self-keying worse — coach takeoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>joshm</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>4684185</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>254884</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>2926320</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>205119</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>1757865</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>49765</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>2.830991003290924</v>
+      </c>
+      <c r="K11" s="27" t="n">
+        <v>4.179008996709076</v>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t>self-keying worse — coach takeoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>carlm</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>4145776</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>198077</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>3986270</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>195754</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>159506</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>2323</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>1.456371547151831</v>
+      </c>
+      <c r="K12" s="27" t="n">
+        <v>3.453628452848169</v>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>self-keying worse — coach takeoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>stevet</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>3925223</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>263528</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>1242665</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>75157</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>2682558</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>188371</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>7.022066251689618</v>
+      </c>
+      <c r="K13" s="27" t="n">
+        <v>-0.9720662516896184</v>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>self ≈ handoff (consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>dustye</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>3234853</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>159408</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>2458092</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>117042</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>776761</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>42366</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>5.454187324028884</v>
+      </c>
+      <c r="K14" s="27" t="n">
+        <v>-0.6941873240288841</v>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>self ≈ handoff (consistent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>austinb</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>2569214</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>192321</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>2371983</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>189804</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>197231</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>2517</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>1.276168553624937</v>
+      </c>
+      <c r="K15" s="27" t="n">
+        <v>6.723831446375063</v>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>self-keying worse — coach takeoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>jacobw</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>2331326</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>117771</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>2013709</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>85831</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>317617</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>31940</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>10.05613679368548</v>
+      </c>
+      <c r="K16" s="27" t="n">
+        <v>-5.796136793685475</v>
+      </c>
+      <c r="L16" s="28" t="inlineStr">
+        <is>
+          <t>handoff penalty — review shipping lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>davea</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>1953875</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>158403</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>1149146</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>121942</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>804729</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>36461</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>4.530842059873573</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>6.079157940126427</v>
+      </c>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
+          <t>self-keying worse — coach takeoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>markt</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>1742086</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>69286</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>1362122</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>39552</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>379964</v>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>29734</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>7.825478203198198</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>-4.925478203198198</v>
+      </c>
+      <c r="L18" s="28" t="inlineStr">
+        <is>
+          <t>handoff penalty — review shipping lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>tj</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="n">
+        <v>1346935</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>110068</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>676497</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>67810</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>670438</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>42258</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>6.303043681891539</v>
+      </c>
+      <c r="K19" s="27" t="n">
+        <v>3.716956318108461</v>
+      </c>
+      <c r="L19" s="21" t="inlineStr">
+        <is>
+          <t>self-keying worse — coach takeoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>steves</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>1310042</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>81414</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>1187937</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>80680</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>122105</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>734</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>0.6011219851766921</v>
+      </c>
+      <c r="K20" s="27" t="n">
+        <v>6.188878014823308</v>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
+        <is>
+          <t>self-keying worse — coach takeoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>mickf</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>1218959</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>86632</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>822619</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>17205</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>396340</v>
+      </c>
+      <c r="I21" s="13" t="n">
+        <v>69427</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>17.51703083211384</v>
+      </c>
+      <c r="K21" s="27" t="n">
+        <v>-15.42703083211384</v>
+      </c>
+      <c r="L21" s="28" t="inlineStr">
+        <is>
+          <t>handoff penalty — review shipping lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>ethans</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n">
+        <v>741091</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>51636</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>722837</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>51040</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>18254</v>
+      </c>
+      <c r="I22" s="13" t="n">
+        <v>596</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>3.265037799934261</v>
+      </c>
+      <c r="K22" s="27" t="n">
+        <v>3.794962200065739</v>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
+          <t>self-keying worse — coach takeoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>isaiahs</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>598198</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>30519</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>273891</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>7767</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>324307</v>
+      </c>
+      <c r="I23" s="13" t="n">
+        <v>22752</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>7.015574748617821</v>
+      </c>
+      <c r="K23" s="27" t="n">
+        <v>-4.175574748617821</v>
+      </c>
+      <c r="L23" s="28" t="inlineStr">
+        <is>
+          <t>handoff penalty — review shipping lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>matte</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>590124</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>41479</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>526487</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>39908</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>63637</v>
+      </c>
+      <c r="I24" s="13" t="n">
+        <v>1571</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>2.468689598818298</v>
+      </c>
+      <c r="K24" s="27" t="n">
+        <v>5.111310401181703</v>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
+        <is>
+          <t>self-keying worse — coach takeoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>jameym</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>443884</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>35382</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>303793</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>27048</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>140091</v>
+      </c>
+      <c r="I25" s="13" t="n">
+        <v>8334</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>5.948990299162687</v>
+      </c>
+      <c r="K25" s="27" t="n">
+        <v>2.951009700837314</v>
+      </c>
+      <c r="L25" s="21" t="inlineStr">
+        <is>
+          <t>self-keying worse — coach takeoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>zachl</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>348331</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>28089</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>254495</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>15078</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>93836</v>
+      </c>
+      <c r="I26" s="13" t="n">
+        <v>13011</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>13.86568054904301</v>
+      </c>
+      <c r="K26" s="27" t="n">
+        <v>-7.945680549043011</v>
+      </c>
+      <c r="L26" s="28" t="inlineStr">
+        <is>
+          <t>handoff penalty — review shipping lists</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="50" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>How to read: 'Self-Keyed' = the rep keyed the SO themselves (rep_1 = rep_3). 'Other-Keyed' = someone else (counter staff, designer, support rep) keyed the SO for their account. Same denominator, split. Diagnostic: 'self-keying worse' → coach the rep on takeoff math. 'handoff penalty' → the shipping list or handoff process is leaking. 'self ≈ handoff' = consistent across methods.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A28:L28"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D5:D26">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="5"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G26">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="5"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:J26">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="5"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>All Order-Writers by rep_3 (real-product SKUs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Includes outside reps writing for themselves + counter staff + designers. Sorted by ship $.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Person (rep_3)</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Ship SOs</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Credit Memos</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Ship $</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Credit $</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Return %</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>garretp</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="n">
+        <v>3167</v>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>606</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>6927273</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>509213</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>7.35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>markg</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>1443</v>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>6551447</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>8790</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>mikes</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>1810</v>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>124</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>4870102</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>114853</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>zacl</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>2850</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>373</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>4638124</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>206579</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>pauln</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>3014</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>653</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>4128778</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>411387</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>9.960000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>carlm</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="n">
+        <v>1713</v>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>349</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>4005255</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>196457</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>justons</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="n">
+        <v>670</v>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>3989398</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>mattb</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="n">
+        <v>2467</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>376</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>3718801</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>302656</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>8.140000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>joshm</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="n">
+        <v>1138</v>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>109</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>3052425</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>210327</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>6.89</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>jacobw</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>236</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>2881516</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>119691</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>4.15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>kevinv</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n">
+        <v>1855</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>247</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>2866144</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>229268</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>dustye</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>1821</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>204</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>2810265</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>143626</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>5.11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>austinb</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="n">
+        <v>1491</v>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>239</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>2527054</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>197359</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>7.81</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>davea</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n">
+        <v>1586</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>303</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>1993605</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>225819</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>11.33</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>evanc</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="n">
+        <v>228</v>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>1964703</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>jameym</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="n">
+        <v>970</v>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>151</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>1841992</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>88427</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>markt</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="n">
+        <v>730</v>
+      </c>
+      <c r="C21" s="18" t="n">
+        <v>70</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>1671767</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>46448</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>stevet</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="n">
+        <v>1242</v>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>202</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>1467559</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>95625</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>6.52</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>steves</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="n">
+        <v>901</v>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>122</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>1414007</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>95854</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>6.78</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>katelynj</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="n">
+        <v>2330</v>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>399</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>1262203</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>162355</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>12.86</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>johnm</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="n">
+        <v>259</v>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>1159764</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>16846</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>andrewg</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="n">
+        <v>874</v>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>296</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>1027673</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>212398</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>20.67</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>ethans</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="n">
+        <v>381</v>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>988433</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>51314</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>michaelas</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="n">
+        <v>2919</v>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>603</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>980608</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>193752</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>19.76</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>mickf</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="n">
+        <v>571</v>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>52</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>937448</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>20203</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>bevw</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="n">
+        <v>1279</v>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>256</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>786281</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>92924</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>11.82</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>tj</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="n">
+        <v>351</v>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>57</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>748551</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>70748</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>9.449999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>zachl</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="n">
+        <v>1385</v>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>88</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>680866</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>26077</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>matte</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="n">
+        <v>363</v>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>95</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>678298</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>45599</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>6.72</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>daveg</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="n">
+        <v>494</v>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>61</v>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>611845</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>16695</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>austins</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="n">
+        <v>611</v>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>42</v>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>565150</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>15774</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>spencerl</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="n">
+        <v>1045</v>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>41</v>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>563577</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>17592</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>emilys</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="n">
+        <v>1141</v>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>199</v>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>557266</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>96192</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>17.26</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>tomn</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="n">
+        <v>380</v>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>553446</v>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>42032</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>daves</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="n">
+        <v>566</v>
+      </c>
+      <c r="C39" s="18" t="n">
+        <v>76</v>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>452915</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>32708</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>7.22</v>
+      </c>
+    </row>
+    <row r="41" ht="50" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>Note: markg, justons, evanc, johnm are designer/project-sales roles keying truss/window/EWP orders — those categories return at &lt;1% by nature, so their books look clean by category mix, not by skill. Real signal is on the counter-staff names (katelynj, michaelas, andrewg, emilys, bevw, bradf) running 12-21% on writing-for-others.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A41:F41"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F5:F39">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="7"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Account Owner (rep_1) → Ticket Writer (rep_3) where they differ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Filter: &gt;$75K shipped on the pair. Real-product SKUs only. Sorted by ship $.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Account Owner (rep_1)</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Keyed By (rep_3)</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Ship SOs</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Credit Memos</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Ship $</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Credit $</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Return %</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>stevet</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>garretp</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>736</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>204</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>1656386</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>153851</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>9.289999999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>zacl</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>justons</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>261</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>1437050</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>zacl</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>jameym</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>678</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>88</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>1362963</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>23904</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>zacl</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>markg</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>367</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>1341189</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>mikes</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>garretp</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>589</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>54</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>886895</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>41241</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>4.65</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>mikes</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>justons</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>134</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>866572</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>mikes</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>markg</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>153</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>836504</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>1057</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>garretp</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>markg</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>137</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>762423</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>katelynj</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>979</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>115</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>606028</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>37819</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>6.24</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>pauln</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>markg</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>91</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>581322</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>joshm</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>markg</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>542470</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>1382</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>stevet</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>markg</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>122</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>528719</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>2472</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>joshm</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>evanc</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>526663</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>mattb</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>markg</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>82</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>451376</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>1161</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>spencerl</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>466</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>402273</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>14333</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>garretp</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>justons</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>73</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>391759</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>bevw</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n">
+        <v>530</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>98</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>376605</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>27331</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>7.26</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>kevinv</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>evanc</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>43</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>370756</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>michaelas</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>1152</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>153</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>338050</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>60492</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>17.89</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>kevinv</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>johnm</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>322845</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>375</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>andrewg</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>260</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>28</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>303274</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>12500</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>kevinv</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>markg</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>73</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>298477</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>davea</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>markg</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>68</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>279928</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>1738</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kevinv</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>justons</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>37</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>276420</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>davea</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>222</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>38</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>272214</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>16935</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>6.22</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>daveg</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>172</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>27</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>272049</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>8397</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>daves</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>258</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>268524</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>6835</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>markg</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>128</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>263075</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>713</v>
+      </c>
+      <c r="G32" s="14" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>joek</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>austins</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>152</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>254524</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>2389</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kevinv</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>andrewg</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>160</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>33</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>246878</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>40465</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <v>16.39</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>pauln</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>evanc</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>241731</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>mattb</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>evanc</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>238565</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>emilys</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>415</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>49</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>235654</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>18729</v>
+      </c>
+      <c r="G37" s="14" t="n">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>zacl</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>jacobw</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>145</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>229227</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>3593</v>
+      </c>
+      <c r="G38" s="14" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>pauln</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>justons</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n">
+        <v>29</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>221760</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>dustye</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>markg</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>48</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>217660</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>267</v>
+      </c>
+      <c r="G40" s="14" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>mattb</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>justons</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>28</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>209660</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>joek</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>michaelas</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>379</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>207439</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>20270</v>
+      </c>
+      <c r="G42" s="14" t="n">
+        <v>9.77</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>garretp</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>stevet</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="n">
+        <v>168</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>206339</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>12455</v>
+      </c>
+      <c r="G43" s="14" t="n">
+        <v>6.04</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>tomn</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="n">
+        <v>201</v>
+      </c>
+      <c r="D44" s="18" t="n">
+        <v>34</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>198153</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>15389</v>
+      </c>
+      <c r="G44" s="14" t="n">
+        <v>7.77</v>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>How to read: Account Owner is on the hook regardless. Keyed By is who entered the SO. The high-return pairs — stevet→garretp ($154K leak at 9.3%), house→michaelas ($60K at 17.9%), kevinv→andrewg ($40K at 16.4%) — are where the shipping list or counter handoff is creating real material come-backs. The clean handoffs (markg, justons, evanc, johnm) are designer/project sales handling truss + window + EWP categories that don't return.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A46:G46"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G5:G44">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="8"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G94"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Per-SKU rep_1 (account-owner) breakdown for top 15 credit-leaking SKUs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Filter on display: rep_1 ship_$ ≥ $15K OR cred_$ ≥ $2K per SKU. Sorted by SKU, then by ship $ desc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>rep_1 (account owner)</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Ship SOs</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Credit Memos</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Ship $</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Credit $</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Return %</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>0106pop</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>mikes</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>247</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>42475</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>5169</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>12.17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>0106pop</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>pauln</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>290</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>95</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>24528</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>5739</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>0106pop</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>kevinv</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>85</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>19554</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>3953</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>20.22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>0106pop</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>zacl</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>228</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>18549</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>1530</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>0106pop</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>garretp</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>130</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>45</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>13907</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>3878</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>27.89</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>0108pop</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>mikes</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>244</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>65</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>41942</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>5486</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>13.08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>0108pop</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>zacl</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>308</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>41130</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>4157</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>10.11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>0108pop</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>pauln</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>273</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>121</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>36494</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>7724</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>21.16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>0108pop</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>garretp</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>168</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>54</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>21457</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>5034</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>23.46</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>0108pop</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>kevinv</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>91</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>19542</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>2411</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>12.34</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>0108pop</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>stevet</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>123</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>29</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>16404</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>2129</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>12.98</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>birchply4834</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>pauln</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>231</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>78</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>58169</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>10752</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>18.48</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>birchply4834</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>garretp</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>144</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>61</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>55019</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>9359</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>17.01</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>birchply4834</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>stevet</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>92</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>35</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>43301</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>9178</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>21.19</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>birchply4834</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>mattb</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>62</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>32871</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>4348</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>13.23</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>birchply4834</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>kevinv</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>31813</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>4542</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>14.28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>birchply4834</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>mikes</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>15009</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>2556</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>17.03</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>birchply4834</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>zacl</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>8795</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>2415</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>27.46</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>clayjamb691617</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>pauln</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>219</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>193</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>66807</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>27561</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>41.25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>clayjamb691617</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>stevet</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>8786</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>3392</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>decktuscc106sblk</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>81</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>42080</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>5946</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>14.13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>decktuscc106sblk</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>stevet</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>52</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>33629</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>3242</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>9.640000000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>decktuscc106sblk</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>carlm</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>39</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>25908</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>2108</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>8.140000000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>decktuscc106sblk</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>markt</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>46</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>25242</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>3509</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>decktuscc106sblk</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>mattb</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>45</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>25102</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>2489</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>9.92</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>decktuscc106sblk</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>pauln</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>36</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>23115</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>224</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>decktuscc106sblk</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>mikes</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>31</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>18165</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>896</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>4.93</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>decktuscc106sblk</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>jacobw</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>32</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>16713</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>5047</v>
+      </c>
+      <c r="G32" s="14" t="n">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>decktuscc106sblk</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>kevinv</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>16646</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>389</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="inlineStr">
+        <is>
+          <t>decktuscc108sblk</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>69</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>44405</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>5354</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <v>12.06</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>decktuscc108sblk</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>markt</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>44</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>33333</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>1107</v>
+      </c>
+      <c r="G35" s="14" t="n">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>decktuscc108sblk</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>stevet</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>29</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>23893</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>6023</v>
+      </c>
+      <c r="G36" s="14" t="n">
+        <v>25.21</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>decktuscc108sblk</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>carlm</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>32</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>20711</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>1714</v>
+      </c>
+      <c r="G37" s="14" t="n">
+        <v>8.27</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>decktuscc108sblk</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>garretp</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>16115</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>decktuscc108sblk</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>mattb</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>15006</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>3507</v>
+      </c>
+      <c r="G39" s="14" t="n">
+        <v>23.37</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>decktuscc108sblk</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>davea</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>12069</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>6009</v>
+      </c>
+      <c r="G40" s="14" t="n">
+        <v>49.78</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="29" t="inlineStr">
+        <is>
+          <t>dowblue48200</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>kevinv</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>28</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>42050</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>750</v>
+      </c>
+      <c r="G41" s="14" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>dowblue48200</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>garretp</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>61</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>34423</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>5953</v>
+      </c>
+      <c r="G42" s="14" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>dowblue48200</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>dustye</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>23031</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>1309</v>
+      </c>
+      <c r="G43" s="14" t="n">
+        <v>5.68</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>dowblue48200</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>stevet</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="D44" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>19212</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>6376</v>
+      </c>
+      <c r="G44" s="14" t="n">
+        <v>33.19</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>dowblue48200</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>zacl</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D45" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>12672</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>2836</v>
+      </c>
+      <c r="G45" s="14" t="n">
+        <v>22.38</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>dowblue48200</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>mattb</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" s="13" t="n">
+        <v>12266</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>3026</v>
+      </c>
+      <c r="G46" s="14" t="n">
+        <v>24.67</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>dowblue48200</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>steves</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>4457</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>2306</v>
+      </c>
+      <c r="G47" s="14" t="n">
+        <v>51.74</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="29" t="inlineStr">
+        <is>
+          <t>gyp4858</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>zacl</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="D48" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="E48" s="13" t="n">
+        <v>108248</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>5671</v>
+      </c>
+      <c r="G48" s="14" t="n">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>gyp4858</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>carlm</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="n">
+        <v>49</v>
+      </c>
+      <c r="D49" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="E49" s="13" t="n">
+        <v>45954</v>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>5883</v>
+      </c>
+      <c r="G49" s="14" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>gyp4858</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>jacobw</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="D50" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>31686</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>1675</v>
+      </c>
+      <c r="G50" s="14" t="n">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>gyp4858</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>austinb</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="n">
+        <v>28</v>
+      </c>
+      <c r="D51" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="13" t="n">
+        <v>25249</v>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>582</v>
+      </c>
+      <c r="G51" s="14" t="n">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>gyp4858</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>kevinv</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="D52" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" s="13" t="n">
+        <v>18043</v>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>2883</v>
+      </c>
+      <c r="G52" s="14" t="n">
+        <v>15.98</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>gyp4858</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>dustye</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="D53" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="13" t="n">
+        <v>17944</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>5462</v>
+      </c>
+      <c r="G53" s="14" t="n">
+        <v>30.44</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>gyp4858</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>mikes</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="D54" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" s="13" t="n">
+        <v>15618</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>3046</v>
+      </c>
+      <c r="G54" s="14" t="n">
+        <v>19.51</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>gyp4858</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>steves</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="D55" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="E55" s="13" t="n">
+        <v>15174</v>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>3542</v>
+      </c>
+      <c r="G55" s="14" t="n">
+        <v>23.34</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="29" t="inlineStr">
+        <is>
+          <t>jhtrimtx44075</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>garretp</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="n">
+        <v>201</v>
+      </c>
+      <c r="D56" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="E56" s="13" t="n">
+        <v>124827</v>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>9865</v>
+      </c>
+      <c r="G56" s="14" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>jhtrimtx44075</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>mikes</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="D57" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="E57" s="13" t="n">
+        <v>40553</v>
+      </c>
+      <c r="F57" s="13" t="n">
+        <v>5180</v>
+      </c>
+      <c r="G57" s="14" t="n">
+        <v>12.77</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>jhtrimtx44075</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>mattb</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n">
+        <v>41</v>
+      </c>
+      <c r="D58" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="E58" s="13" t="n">
+        <v>38898</v>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>11852</v>
+      </c>
+      <c r="G58" s="14" t="n">
+        <v>30.47</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>jhtrimtx44075</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>kevinv</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="n">
+        <v>43</v>
+      </c>
+      <c r="D59" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="E59" s="13" t="n">
+        <v>32648</v>
+      </c>
+      <c r="F59" s="13" t="n">
+        <v>5760</v>
+      </c>
+      <c r="G59" s="14" t="n">
+        <v>17.64</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>jhtrimtx44075</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>stevet</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="n">
+        <v>82</v>
+      </c>
+      <c r="D60" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="E60" s="13" t="n">
+        <v>32314</v>
+      </c>
+      <c r="F60" s="13" t="n">
+        <v>2329</v>
+      </c>
+      <c r="G60" s="14" t="n">
+        <v>7.21</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>jhtrimtx44075</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>davea</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="13" t="n">
+        <v>4805</v>
+      </c>
+      <c r="F61" s="13" t="n">
+        <v>2730</v>
+      </c>
+      <c r="G61" s="14" t="n">
+        <v>56.82</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="29" t="inlineStr">
+        <is>
+          <t>lpshake7161248st</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>mikes</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="n">
+        <v>61</v>
+      </c>
+      <c r="D62" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="E62" s="13" t="n">
+        <v>42730</v>
+      </c>
+      <c r="F62" s="13" t="n">
+        <v>9545</v>
+      </c>
+      <c r="G62" s="14" t="n">
+        <v>22.34</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>lpshake7161248st</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>pauln</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n">
+        <v>27</v>
+      </c>
+      <c r="D63" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="E63" s="13" t="n">
+        <v>27250</v>
+      </c>
+      <c r="F63" s="13" t="n">
+        <v>6595</v>
+      </c>
+      <c r="G63" s="14" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>lpshake7161248st</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>davea</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D64" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" s="13" t="n">
+        <v>11102</v>
+      </c>
+      <c r="F64" s="13" t="n">
+        <v>3128</v>
+      </c>
+      <c r="G64" s="14" t="n">
+        <v>28.17</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>lpshake7161248st</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>kevinv</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D65" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" s="13" t="n">
+        <v>8158</v>
+      </c>
+      <c r="F65" s="13" t="n">
+        <v>3090</v>
+      </c>
+      <c r="G65" s="14" t="n">
+        <v>37.88</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>lptrimtxt010816</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>mikes</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="n">
+        <v>193</v>
+      </c>
+      <c r="D66" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="E66" s="13" t="n">
+        <v>112304</v>
+      </c>
+      <c r="F66" s="13" t="n">
+        <v>5678</v>
+      </c>
+      <c r="G66" s="14" t="n">
+        <v>5.06</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>lptrimtxt010816</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>pauln</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="n">
+        <v>93</v>
+      </c>
+      <c r="D67" s="18" t="n">
+        <v>34</v>
+      </c>
+      <c r="E67" s="13" t="n">
+        <v>46458</v>
+      </c>
+      <c r="F67" s="13" t="n">
+        <v>9388</v>
+      </c>
+      <c r="G67" s="14" t="n">
+        <v>20.21</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>lptrimtxt010816</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>kevinv</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="n">
+        <v>72</v>
+      </c>
+      <c r="D68" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="E68" s="13" t="n">
+        <v>32479</v>
+      </c>
+      <c r="F68" s="13" t="n">
+        <v>6466</v>
+      </c>
+      <c r="G68" s="14" t="n">
+        <v>19.91</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>lptrimtxt010816</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>zacl</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="n">
+        <v>125</v>
+      </c>
+      <c r="D69" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="E69" s="13" t="n">
+        <v>28775</v>
+      </c>
+      <c r="F69" s="13" t="n">
+        <v>5638</v>
+      </c>
+      <c r="G69" s="14" t="n">
+        <v>19.59</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>lptrimtxt010816</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>mattb</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="D70" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="E70" s="13" t="n">
+        <v>27884</v>
+      </c>
+      <c r="F70" s="13" t="n">
+        <v>9583</v>
+      </c>
+      <c r="G70" s="14" t="n">
+        <v>34.37</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>lptrimtxt010816</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>dustye</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="n">
+        <v>37</v>
+      </c>
+      <c r="D71" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E71" s="13" t="n">
+        <v>15196</v>
+      </c>
+      <c r="F71" s="13" t="n">
+        <v>2107</v>
+      </c>
+      <c r="G71" s="14" t="n">
+        <v>13.87</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>lptrimtxt010816</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>tj</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="D72" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="E72" s="13" t="n">
+        <v>14176</v>
+      </c>
+      <c r="F72" s="13" t="n">
+        <v>3719</v>
+      </c>
+      <c r="G72" s="14" t="n">
+        <v>26.24</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>lptrimtxt010816</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>joshm</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="D73" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E73" s="13" t="n">
+        <v>13502</v>
+      </c>
+      <c r="F73" s="13" t="n">
+        <v>2578</v>
+      </c>
+      <c r="G73" s="14" t="n">
+        <v>19.09</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
+        <is>
+          <t>lptrimtxt540616</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>mikes</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="n">
+        <v>156</v>
+      </c>
+      <c r="D74" s="18" t="n">
+        <v>51</v>
+      </c>
+      <c r="E74" s="13" t="n">
+        <v>104881</v>
+      </c>
+      <c r="F74" s="13" t="n">
+        <v>8347</v>
+      </c>
+      <c r="G74" s="14" t="n">
+        <v>7.96</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>lptrimtxt540616</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>pauln</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="n">
+        <v>115</v>
+      </c>
+      <c r="D75" s="18" t="n">
+        <v>51</v>
+      </c>
+      <c r="E75" s="13" t="n">
+        <v>64778</v>
+      </c>
+      <c r="F75" s="13" t="n">
+        <v>10842</v>
+      </c>
+      <c r="G75" s="14" t="n">
+        <v>16.74</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>lptrimtxt540616</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>kevinv</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="n">
+        <v>55</v>
+      </c>
+      <c r="D76" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="E76" s="13" t="n">
+        <v>30651</v>
+      </c>
+      <c r="F76" s="13" t="n">
+        <v>3719</v>
+      </c>
+      <c r="G76" s="14" t="n">
+        <v>12.13</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>lptrimtxt540616</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>mattb</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="n">
+        <v>57</v>
+      </c>
+      <c r="D77" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="E77" s="13" t="n">
+        <v>22511</v>
+      </c>
+      <c r="F77" s="13" t="n">
+        <v>3007</v>
+      </c>
+      <c r="G77" s="14" t="n">
+        <v>13.36</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>lptrimtxt540616</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>davea</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="n">
+        <v>39</v>
+      </c>
+      <c r="D78" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E78" s="13" t="n">
+        <v>17574</v>
+      </c>
+      <c r="F78" s="13" t="n">
+        <v>2476</v>
+      </c>
+      <c r="G78" s="14" t="n">
+        <v>14.09</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>lptrimtxt540616</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>joshm</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="D79" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E79" s="13" t="n">
+        <v>15194</v>
+      </c>
+      <c r="F79" s="13" t="n">
+        <v>4089</v>
+      </c>
+      <c r="G79" s="14" t="n">
+        <v>26.91</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="29" t="inlineStr">
+        <is>
+          <t>mdfbase512Ee1e</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>mikes</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="n">
+        <v>184</v>
+      </c>
+      <c r="D80" s="18" t="n">
+        <v>118</v>
+      </c>
+      <c r="E80" s="13" t="n">
+        <v>63883</v>
+      </c>
+      <c r="F80" s="13" t="n">
+        <v>9537</v>
+      </c>
+      <c r="G80" s="14" t="n">
+        <v>14.93</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>mdfbase512Ee1e</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>pauln</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="n">
+        <v>113</v>
+      </c>
+      <c r="D81" s="18" t="n">
+        <v>68</v>
+      </c>
+      <c r="E81" s="13" t="n">
+        <v>33970</v>
+      </c>
+      <c r="F81" s="13" t="n">
+        <v>5785</v>
+      </c>
+      <c r="G81" s="14" t="n">
+        <v>17.03</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>mdfbase512Ee1e</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>zacl</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="n">
+        <v>96</v>
+      </c>
+      <c r="D82" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="E82" s="13" t="n">
+        <v>29143</v>
+      </c>
+      <c r="F82" s="13" t="n">
+        <v>2245</v>
+      </c>
+      <c r="G82" s="14" t="n">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>mdfbase512Ee1e</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>garretp</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="n">
+        <v>79</v>
+      </c>
+      <c r="D83" s="18" t="n">
+        <v>43</v>
+      </c>
+      <c r="E83" s="13" t="n">
+        <v>28055</v>
+      </c>
+      <c r="F83" s="13" t="n">
+        <v>5897</v>
+      </c>
+      <c r="G83" s="14" t="n">
+        <v>21.02</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>mdfbase512Ee1e</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>stevet</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="n">
+        <v>103</v>
+      </c>
+      <c r="D84" s="18" t="n">
+        <v>61</v>
+      </c>
+      <c r="E84" s="13" t="n">
+        <v>27491</v>
+      </c>
+      <c r="F84" s="13" t="n">
+        <v>7441</v>
+      </c>
+      <c r="G84" s="14" t="n">
+        <v>27.07</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>mdfbase512Ee1e</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>mattb</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="D85" s="18" t="n">
+        <v>36</v>
+      </c>
+      <c r="E85" s="13" t="n">
+        <v>21759</v>
+      </c>
+      <c r="F85" s="13" t="n">
+        <v>4078</v>
+      </c>
+      <c r="G85" s="14" t="n">
+        <v>18.74</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="29" t="inlineStr">
+        <is>
+          <t>popplypwvc4834</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>mikes</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="n">
+        <v>273</v>
+      </c>
+      <c r="D86" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="E86" s="13" t="n">
+        <v>138833</v>
+      </c>
+      <c r="F86" s="13" t="n">
+        <v>12957</v>
+      </c>
+      <c r="G86" s="14" t="n">
+        <v>9.33</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>popplypwvc4834</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>zacl</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="n">
+        <v>229</v>
+      </c>
+      <c r="D87" s="18" t="n">
+        <v>70</v>
+      </c>
+      <c r="E87" s="13" t="n">
+        <v>90026</v>
+      </c>
+      <c r="F87" s="13" t="n">
+        <v>18295</v>
+      </c>
+      <c r="G87" s="14" t="n">
+        <v>20.32</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>popplypwvc4834</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>mattb</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="n">
+        <v>38</v>
+      </c>
+      <c r="D88" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E88" s="13" t="n">
+        <v>22208</v>
+      </c>
+      <c r="F88" s="13" t="n">
+        <v>1001</v>
+      </c>
+      <c r="G88" s="14" t="n">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>popplypwvc4834</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>garretp</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="D89" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="E89" s="13" t="n">
+        <v>10167</v>
+      </c>
+      <c r="F89" s="13" t="n">
+        <v>4653</v>
+      </c>
+      <c r="G89" s="14" t="n">
+        <v>45.76</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="29" t="inlineStr">
+        <is>
+          <t>pvctrim2212</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>garretp</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="D90" s="18" t="n">
+        <v>52</v>
+      </c>
+      <c r="E90" s="13" t="n">
+        <v>25011</v>
+      </c>
+      <c r="F90" s="13" t="n">
+        <v>6761</v>
+      </c>
+      <c r="G90" s="14" t="n">
+        <v>27.03</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>pvctrim2212</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>pauln</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="n">
+        <v>63</v>
+      </c>
+      <c r="D91" s="18" t="n">
+        <v>31</v>
+      </c>
+      <c r="E91" s="13" t="n">
+        <v>21072</v>
+      </c>
+      <c r="F91" s="13" t="n">
+        <v>3951</v>
+      </c>
+      <c r="G91" s="14" t="n">
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>pvctrim2212</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t>kevinv</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="n">
+        <v>41</v>
+      </c>
+      <c r="D92" s="18" t="n">
+        <v>34</v>
+      </c>
+      <c r="E92" s="13" t="n">
+        <v>17518</v>
+      </c>
+      <c r="F92" s="13" t="n">
+        <v>6658</v>
+      </c>
+      <c r="G92" s="14" t="n">
+        <v>38.01</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>pvctrim2212</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>mattb</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="n">
+        <v>32</v>
+      </c>
+      <c r="D93" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="E93" s="13" t="n">
+        <v>13043</v>
+      </c>
+      <c r="F93" s="13" t="n">
+        <v>3230</v>
+      </c>
+      <c r="G93" s="14" t="n">
+        <v>24.76</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>pvctrim2212</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>stevet</t>
+        </is>
+      </c>
+      <c r="C94" s="18" t="n">
+        <v>37</v>
+      </c>
+      <c r="D94" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="E94" s="13" t="n">
+        <v>11188</v>
+      </c>
+      <c r="F94" s="13" t="n">
+        <v>3043</v>
+      </c>
+      <c r="G94" s="14" t="n">
+        <v>27.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="G5:G94">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="15"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
